--- a/Zoomlion/ZA14JE.xlsx
+++ b/Zoomlion/ZA14JE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,33 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E394"/>
+  <dimension ref="A1:F394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Material No.</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Item and Spec</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Models</t>
         </is>
       </c>
     </row>
@@ -463,6 +480,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -484,6 +506,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -505,6 +532,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -526,6 +558,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,7 +575,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dam-boardⅠ</t>
+          <t>Dam-boardI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -547,6 +584,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -568,6 +610,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -589,6 +636,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -610,6 +662,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -631,6 +688,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -643,7 +705,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Anti-drop plateⅡ</t>
+          <t>Anti-drop plateII</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -652,6 +714,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -673,6 +740,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -694,6 +766,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -715,6 +792,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -736,6 +818,11 @@
           <t>Jib 00773400210000000; Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -757,6 +844,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -778,6 +870,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -799,6 +896,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -820,6 +922,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -841,6 +948,11 @@
           <t>Jib 00773400210000000; Upper Boom Assembly 00773400310000000; Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -862,6 +974,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -883,6 +1000,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -904,6 +1026,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -925,6 +1052,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -946,6 +1078,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -967,6 +1104,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -988,6 +1130,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1009,6 +1156,11 @@
           <t>Upper Boom Assembly 00773400310000000; Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1030,6 +1182,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1051,6 +1208,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1072,6 +1234,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1093,6 +1260,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1114,6 +1286,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1135,6 +1312,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1156,6 +1338,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1177,6 +1364,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1198,6 +1390,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1219,6 +1416,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1240,6 +1442,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1261,6 +1468,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1282,6 +1494,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1303,6 +1520,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1324,6 +1546,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1345,6 +1572,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1366,6 +1598,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1387,6 +1624,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1408,6 +1650,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1429,6 +1676,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1450,6 +1702,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1471,6 +1728,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1492,6 +1754,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1513,6 +1780,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1534,6 +1806,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1555,6 +1832,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1576,6 +1858,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1597,6 +1884,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1618,6 +1910,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1639,6 +1936,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1660,6 +1962,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1681,6 +1988,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1702,6 +2014,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1723,6 +2040,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1744,6 +2066,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1765,6 +2092,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1786,6 +2118,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1807,6 +2144,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1828,6 +2170,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1849,6 +2196,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1870,6 +2222,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1891,6 +2248,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1912,6 +2274,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1933,6 +2300,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1954,6 +2326,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1975,6 +2352,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1996,6 +2378,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2017,6 +2404,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2038,6 +2430,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2059,6 +2456,11 @@
           <t>Tower Boom Assembly 00773400410000000; Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2080,6 +2482,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2101,6 +2508,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2122,6 +2534,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2143,6 +2560,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2164,6 +2586,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2185,6 +2612,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2206,6 +2638,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2227,6 +2664,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2248,6 +2690,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2269,6 +2716,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2290,6 +2742,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2311,6 +2768,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2332,6 +2794,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2353,6 +2820,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2374,6 +2846,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2395,6 +2872,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2416,6 +2898,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2437,6 +2924,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2458,6 +2950,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2479,6 +2976,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2500,6 +3002,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2521,6 +3028,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2542,6 +3054,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2563,6 +3080,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2588,6 +3110,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2609,6 +3136,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2630,6 +3162,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2651,6 +3188,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2672,6 +3214,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2693,6 +3240,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2714,6 +3266,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2735,6 +3292,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2756,6 +3318,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2777,6 +3344,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2798,6 +3370,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2819,6 +3396,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2840,6 +3422,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2861,6 +3448,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2882,6 +3474,11 @@
           <t>Counterweight 00773401010000000</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2903,6 +3500,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2924,6 +3526,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2945,6 +3552,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2966,6 +3578,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2987,6 +3604,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3008,6 +3630,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3029,6 +3656,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3050,6 +3682,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3071,6 +3708,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3092,6 +3734,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3113,6 +3760,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3134,6 +3786,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3155,6 +3812,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3176,6 +3838,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3197,6 +3864,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3218,6 +3890,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3239,6 +3916,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3260,6 +3942,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3281,6 +3968,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3302,6 +3994,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3323,6 +4020,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3344,6 +4046,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3365,6 +4072,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3386,6 +4098,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3398,11 +4115,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Hub 
-assembly- 
-right 
-steering 
-knuckle</t>
+          <t>Hub assembly- right steering knuckle</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -3411,6 +4124,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3432,6 +4150,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3453,6 +4176,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3474,6 +4202,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3486,8 +4219,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Centre revolving joint- bracket 
-welds</t>
+          <t>Centre revolving joint- bracket welds</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -3496,6 +4228,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3508,7 +4245,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chassis counterweight Ⅱ</t>
+          <t>Chassis counterweight II</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -3517,6 +4254,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3538,6 +4280,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3559,6 +4306,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3580,6 +4332,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3601,6 +4358,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3622,6 +4384,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3634,10 +4401,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Platform 
-electrical 
-control 
-box assembly</t>
+          <t>Platform electrical control box assembly</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -3646,6 +4410,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3658,8 +4427,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Functional pump- driver B+ to 
-functional pump A2</t>
+          <t>Functional pump- driver B+ to functional pump A2</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -3668,6 +4436,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3680,8 +4453,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Functional pump- driver M to 
-functional pump D2</t>
+          <t>Functional pump- driver M to functional pump D2</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -3690,6 +4462,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3702,8 +4479,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Functional pump-D1 to 与 A1 
-wiring</t>
+          <t>Functional pump-D1 to 与 A1 wiring</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -3712,6 +4488,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3724,8 +4505,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Battery positive pole to manual 
-switch wiring</t>
+          <t>Battery positive pole to manual switch wiring</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
@@ -3734,6 +4514,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3746,8 +4531,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Manual switch to wire spool positive 
-pole wiring</t>
+          <t>Manual switch to wire spool positive pole wiring</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
@@ -3756,6 +4540,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3768,8 +4557,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Battery negative pole to wire spool 
-negative pole</t>
+          <t>Battery negative pole to wire spool negative pole</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -3778,6 +4566,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3799,6 +4592,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3811,8 +4609,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Brake OUT to spool B﹢-right 
-wiring</t>
+          <t>Brake OUT to spool B﹢-right wiring</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -3821,6 +4618,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3842,6 +4644,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3854,8 +4661,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Emergency battery positive pole to 
-auxiliary pump positive pump</t>
+          <t>Emergency battery positive pole to auxiliary pump positive pump</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -3864,6 +4670,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3876,8 +4687,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Emergency pump negative pole to 
-auxiliary pump negative pole</t>
+          <t>Emergency pump negative pole to auxiliary pump negative pole</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -3886,6 +4696,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3907,6 +4722,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3928,6 +4748,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3949,6 +4774,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3970,6 +4800,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3991,6 +4826,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4012,6 +4852,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -4033,6 +4878,11 @@
           <t>Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -4058,6 +4908,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -4079,6 +4934,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4100,6 +4960,11 @@
           <t>Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4121,6 +4986,11 @@
           <t>Telescopic Select-valve Assembly 00773405212400000</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4142,6 +5012,11 @@
           <t>Upper Leveling Cylinder CBV Assembly 00773405213000000; Jib Cylinder CBV Assembly 00773405213200000</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4163,6 +5038,11 @@
           <t>Telescopic Cylinder CBV Assembly 00773405213800000</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4184,6 +5064,11 @@
           <t>Platform Select-valve Assembly 00773405211200000</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -4205,6 +5090,11 @@
           <t>Lower Leveling Cylinder CBV Assembly 00773405212800000</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4226,6 +5116,11 @@
           <t>Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -4247,6 +5142,11 @@
           <t>Steering Priority Valve Assembly 00773405215000000</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -4268,6 +5168,11 @@
           <t>Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4289,6 +5194,11 @@
           <t>High Pressure Filter Assembly 0077340521100000</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4310,6 +5220,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4331,6 +5246,11 @@
           <t>Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4352,6 +5272,11 @@
           <t>Platform Select-valve Assembly 00773405211200000</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4373,6 +5298,11 @@
           <t>Main Valve Assembly 00773405251600000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4394,6 +5324,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4415,6 +5350,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4440,6 +5380,11 @@
           <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4461,6 +5406,11 @@
           <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4482,6 +5432,11 @@
           <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4503,6 +5458,11 @@
           <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4528,6 +5488,11 @@
           <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4549,6 +5514,11 @@
           <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4570,6 +5540,11 @@
           <t>Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4591,6 +5566,11 @@
           <t>Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4612,6 +5592,11 @@
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4633,6 +5618,11 @@
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4654,6 +5644,11 @@
           <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4666,9 +5661,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Limit switch (outside)- steering 
-angle; Limit switch (inside)- steering 
-angle; Boom length limit switch 1; Boom length limit switch 2</t>
+          <t>Limit switch (outside)- steering angle; Limit switch (inside)- steering angle; Boom length limit switch 1; Boom length limit switch 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -4677,6 +5670,11 @@
           <t>Turntable Electric Cables 00773406230230011; Boom Electric Cables 00773406230230031</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4694,13 +5692,17 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Emergency stop 
-switch</t>
+          <t>Emergency stop switch</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -4720,13 +5722,17 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Driving 
-orienteering</t>
+          <t>Driving orienteering</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -4746,15 +5752,17 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Platform rotating; Platform leveling; Jib lifting; Boom telescoping; Boom lifting; Tower boom 
-lifting; Turntable rotary; Emergency power 
-and enables; Platform rotary 
-switch; Jib lifting switch; Jib telescoping</t>
+          <t>Platform rotating; Platform leveling; Jib lifting; Boom telescoping; Boom lifting; Tower boom lifting; Turntable rotary; Emergency power and enables; Platform rotary switch; Jib lifting switch; Jib telescoping</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -4774,14 +5782,17 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Travel speed 
-control; Platform leveling 
-control</t>
+          <t>Travel speed control; Platform leveling control</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -4809,6 +5820,11 @@
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4830,6 +5846,11 @@
           <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4851,6 +5872,11 @@
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4872,6 +5898,11 @@
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4893,6 +5924,11 @@
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4914,6 +5950,11 @@
           <t>Work Platform 00773400120000000; Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4935,6 +5976,11 @@
           <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4952,14 +5998,17 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Plug-in slip ring 2; Negative or 
-positive of power 
-source</t>
+          <t>Plug-in slip ring 2; Negative or positive of power source</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>Turntable Electric Cables 00773406230230011; Chassis Electric Cables 00773406230420000</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -4983,6 +6032,11 @@
           <t>Boom Electric Cables 00773406230230031</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -5008,6 +6062,11 @@
           <t>Turntable Electric Cables 00773406230230011; Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -5020,30 +6079,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>/; Speed control valve- tower boom 
-lowering; Telescopic leveling selection 
-valve; Speed control valve- main boom 
-lowering; sheath</t>
+          <t>/; Speed control valve- tower boom lowering; Telescopic leveling selection valve; Speed control valve- main boom lowering; sheath</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Reversing valve 1-
-Jib rotary; Turntable right-turn 
-valve; Reversing valve 2- 
-expanding and 
-leveling; Turntable left-turn 
-valve; Reversing valve 1-
-expanding and 
-leveling; Lifting valve-main 
-boom; Lifting valve-tower 
-boom; Work light; Charger; Jib lifting 
-selection valve</t>
+          <t>Reversing valve 1- Jib rotary; Turntable right-turn valve; Reversing valve 2- expanding and leveling; Turntable left-turn valve; Reversing valve 1- expanding and leveling; Lifting valve-main boom; Lifting valve-tower boom; Work light; Charger; Jib lifting selection valve</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>Turntable Electric Cables 00773406230230011; Boom Electric Cables 00773406230230031; Chassis Electric Cables 00773406230420000; Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5063,13 +6114,17 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Charger 
-communication</t>
+          <t>Charger communication</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>Chassis Electric Cables 00773406230420000</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5089,13 +6144,17 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Anti-extrusion 
-switch</t>
+          <t>Anti-extrusion switch</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5123,6 +6182,11 @@
           <t>Turntable Electric Cables 00773406230230011; Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -5144,6 +6208,11 @@
           <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5169,6 +6238,11 @@
           <t>Turntable Electric Cables 00773406230230011; Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5186,13 +6260,17 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Platform Electric 
-Cables</t>
+          <t>Platform Electric Cables</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5207,22 +6285,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Deutsch connector; Limit switch- tower boom 
-stowed 1; Limit switch- tower boom 
-stowed 2</t>
+          <t>Deutsch connector; Limit switch- tower boom stowed 1; Limit switch- tower boom stowed 2</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Chain electric 
-cables; Boom Electric 
-Cables; Lift switch-tower 
-boom lifting</t>
+          <t>Chain electric cables; Boom Electric Cables; Lift switch-tower boom lifting</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>Platform Electrical Control Box Assembly 00773406230210000; Turntable Electric Cables 00773406230230011</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5246,6 +6324,11 @@
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -5267,6 +6350,11 @@
           <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5292,6 +6380,11 @@
           <t>Boom Electric Cables 00773406230230031</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -5313,6 +6406,11 @@
           <t>Work Platform 00773400120000000; Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -5334,6 +6432,11 @@
           <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -5351,13 +6454,17 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Frame angle 
-sensor</t>
+          <t>Frame angle sensor</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>Boom Electric Cables 00773406230230031; Chassis Electric Cables 00773406230420000</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5377,13 +6484,17 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Platform plug 
-connector</t>
+          <t>Platform plug connector</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5411,6 +6522,11 @@
           <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -5428,13 +6544,17 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Turntable electric 
-control box</t>
+          <t>Turntable electric control box</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>Boom Electric Cables 00773406230230031</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5458,6 +6578,11 @@
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -5483,6 +6608,11 @@
           <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -5500,13 +6630,17 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Steering angle 
-sensor</t>
+          <t>Steering angle sensor</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>Chassis Electric Cables 00773406230420000</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5530,6 +6664,11 @@
           <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -5551,6 +6690,11 @@
           <t>Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -5572,6 +6716,11 @@
           <t>Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -5589,14 +6738,17 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Boom Electric 
-Cables; Turntable Electric 
-Cables</t>
+          <t>Boom Electric Cables; Turntable Electric Cables</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5616,13 +6768,17 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Turntable electric 
-control box</t>
+          <t>Turntable electric control box</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>Turntable Electric Cables 00773406230230011</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5642,13 +6798,17 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Turntable electric 
-control box</t>
+          <t>Turntable electric control box</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>Turntable Electric Cables 00773406230230011</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5668,13 +6828,17 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Turntable Electric 
-Cables</t>
+          <t>Turntable Electric Cables</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5694,14 +6858,17 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Upper plug-in of 
-chain; Lower plug-in of 
-chain</t>
+          <t>Upper plug-in of chain; Lower plug-in of chain</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -5725,6 +6892,11 @@
           <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5746,6 +6918,11 @@
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5767,6 +6944,11 @@
           <t>Slewing Mechanism 00773400900000000</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5788,6 +6970,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5809,6 +6996,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5834,6 +7026,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5859,6 +7056,11 @@
           <t>Slewing Mechanism 00773400900000000</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5884,6 +7086,11 @@
           <t>Work Platform 00773400120000000; Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5909,6 +7116,11 @@
           <t>Upper Boom Assembly 00773400310000000; Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5934,6 +7146,11 @@
           <t>Upper Boom Assembly 00773400310000000; Turntable 00773400820000000; Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5959,6 +7176,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5984,6 +7206,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -6009,6 +7236,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6034,6 +7266,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6059,6 +7296,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -6071,8 +7313,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Hexagon socket head cap screw 
-M8×20-12.9</t>
+          <t>Hexagon socket head cap screw M8×20-12.9</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6083,6 +7324,11 @@
       <c r="E259" t="inlineStr">
         <is>
           <t>Turntable 00773400820000000</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>
@@ -6110,6 +7356,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -6135,6 +7386,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -6160,6 +7416,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6185,6 +7446,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -6210,6 +7476,11 @@
           <t>Counterweight 00773401010000000</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6235,6 +7506,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -6260,6 +7536,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -6285,6 +7566,11 @@
           <t>Upper Boom Assembly 00773400310000000; Turntable 00773400820000000; Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -6310,6 +7596,11 @@
           <t>Upper Boom Assembly 00773400310000000; Chain System 00773400710000000; Hood 00773401110000000; Hydraulic Tank Assembly 00773405210200000; Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -6335,6 +7626,11 @@
           <t>Turntable 00773400820000000; Chassis 00773402830000000; Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -6360,6 +7656,11 @@
           <t>Chain System 00773400710000000; Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -6385,6 +7686,11 @@
           <t>Turntable 00773400820000000; Chassis 00773402830000000; Steering Priority Valve Assembly 00773405215000000</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -6410,6 +7716,11 @@
           <t>Upper Leveling Cylinder CBV Assembly 00773405213000000</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -6435,6 +7746,11 @@
           <t>Lower Leveling Cylinder CBV Assembly 00773405212800000</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -6460,6 +7776,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -6485,6 +7806,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -6510,6 +7836,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -6535,6 +7866,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -6560,6 +7896,11 @@
           <t>Upper Boom Assembly 00773400310000000; Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -6585,6 +7926,11 @@
           <t>Tower Boom Assembly 00773400410000000; Turntable 00773400820000000; Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -6610,6 +7956,11 @@
           <t>Turntable 00773400820000000; Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -6635,6 +7986,11 @@
           <t>Counterweight 00773401010000000</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -6660,6 +8016,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -6685,6 +8046,11 @@
           <t>Tower Boom Assembly 00773400410000000; Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -6710,6 +8076,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -6735,6 +8106,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -6760,6 +8136,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -6785,6 +8166,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -6810,6 +8196,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -6835,6 +8226,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -6860,6 +8256,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -6885,6 +8286,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -6910,6 +8316,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -6935,6 +8346,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6960,6 +8376,11 @@
           <t>High Pressure Filter Assembly 0077340521100000</t>
         </is>
       </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6985,6 +8406,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -7010,6 +8436,11 @@
           <t>Jib Cylinder CBV Assembly 00773405213200000; Telescopic Cylinder CBV Assembly 00773405213800000</t>
         </is>
       </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -7035,6 +8466,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -7060,6 +8496,11 @@
           <t>Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -7085,6 +8526,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -7110,6 +8556,11 @@
           <t>Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -7135,6 +8586,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7160,6 +8616,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -7185,6 +8646,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -7210,6 +8676,11 @@
           <t>Tower Boom Assembly 00773400410000000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
         </is>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -7235,6 +8706,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -7260,6 +8736,11 @@
           <t>Work Platform 00773400120000000; Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7285,6 +8766,11 @@
           <t>Platform Select-valve Assembly 00773405211200000</t>
         </is>
       </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -7310,6 +8796,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -7335,6 +8826,11 @@
           <t>Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -7360,6 +8856,11 @@
           <t>Telescopic Select-valve Assembly 00773405212400000</t>
         </is>
       </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -7385,6 +8886,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -7410,6 +8916,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -7435,6 +8946,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -7460,6 +8976,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -7485,6 +9006,11 @@
           <t>Chain System 00773400710000000; Turntable 00773400820000000; Hood 00773401110000000; Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -7510,6 +9036,11 @@
           <t>Work Platform 00773400120000000; Jib 00773400210000000</t>
         </is>
       </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -7535,6 +9066,11 @@
           <t>Work Platform 00773400120000000; Jib 00773400210000000; Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -7560,6 +9096,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -7585,6 +9126,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -7610,6 +9156,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -7635,6 +9186,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -7660,6 +9216,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -7685,6 +9246,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -7710,6 +9276,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -7735,6 +9306,11 @@
           <t>Work Platform 00773400120000000</t>
         </is>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -7760,6 +9336,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -7785,6 +9366,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -7810,6 +9396,11 @@
           <t>Platform Select-valve Assembly 00773405211200000; Telescopic Select-valve Assembly 00773405212400000</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -7835,6 +9426,11 @@
           <t>Slewing Mechanism 00773400900000000</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -7860,6 +9456,11 @@
           <t>Work Platform 00773400120000000; Turntable 00773400820000000</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -7885,6 +9486,11 @@
           <t>Work Platform 00773400120000000; Tower Boom Assembly 00773400410000000; Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -7910,6 +9516,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000; Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -7935,6 +9546,11 @@
           <t>Chain System 00773400710000000; High Pressure Filter Assembly 0077340521100000; Lower Leveling Cylinder CBV Assembly 00773405212800000; Upper Leveling Cylinder CBV Assembly 00773405213000000; Jib Cylinder CBV Assembly 00773405213200000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000; Telescopic Cylinder CBV Assembly 00773405213800000</t>
         </is>
       </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -7960,6 +9576,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -7985,6 +9606,11 @@
           <t>Counterweight 00773401010000000</t>
         </is>
       </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -8010,6 +9636,11 @@
           <t>Work Platform 00773400120000000; Upper Boom Assembly 00773400310000000; Chain System 00773400710000000; Tower Boom Assembly 00773400410000000; Turntable 00773400820000000; Hood 00773401110000000; Chassis 00773402830000000; Hydraulic Tank Assembly 00773405210200000; Steering Priority Valve Assembly 00773405215000000; Central Revolving Joint Assembly 00773405210800000; High Pressure Filter Assembly 0077340521100000; Main Valve Assembly 00773405251600000; Jib Cylinder CBV Assembly 00773405213200000</t>
         </is>
       </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -8035,6 +9666,11 @@
           <t>Turntable 00773400820000000; Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -8060,6 +9696,11 @@
           <t>Counterweight 00773401010000000</t>
         </is>
       </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -8085,6 +9726,11 @@
           <t>Work Platform 00773400120000000; Jib 00773400210000000; Upper Boom Assembly 00773400310000000; Tower Boom Assembly 00773400410000000; Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -8110,6 +9756,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -8135,6 +9786,11 @@
           <t>Work Platform 00773400120000000; Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -8160,6 +9816,11 @@
           <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -8185,6 +9846,11 @@
           <t>Work Platform 00773400120000000; Turntable 00773400820000000; Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -8210,6 +9876,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8235,6 +9906,11 @@
           <t>Work Platform 00773400120000000; Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -8260,6 +9936,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -8281,6 +9962,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8302,6 +9988,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -8323,6 +10014,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8344,6 +10040,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -8365,6 +10066,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -8386,6 +10092,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -8407,6 +10118,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -8428,6 +10144,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -8449,6 +10170,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -8470,6 +10196,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -8491,6 +10222,11 @@
           <t>Chain System 00773400710000000</t>
         </is>
       </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -8512,6 +10248,11 @@
           <t>Hood 00773401110000000</t>
         </is>
       </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -8533,6 +10274,11 @@
           <t>Steering Priority Valve Assembly 00773405215000000; Platform Select-valve Assembly 00773405211200000; Telescopic Select-valve Assembly 00773405212400000</t>
         </is>
       </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -8554,6 +10300,11 @@
           <t>Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -8575,6 +10326,11 @@
           <t>Steering Priority Valve Assembly 00773405215000000; Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -8596,6 +10352,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -8617,6 +10378,11 @@
           <t>Lower Leveling Cylinder CBV Assembly 00773405212800000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000; Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -8638,6 +10404,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000; Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -8659,6 +10430,11 @@
           <t>Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -8680,6 +10456,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -8701,6 +10482,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000; Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -8722,6 +10508,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -8743,6 +10534,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -8764,6 +10560,11 @@
           <t>Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -8785,6 +10586,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -8806,6 +10612,11 @@
           <t>Telescopic Cylinder CBV Assembly 00773405213800000</t>
         </is>
       </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -8827,6 +10638,11 @@
           <t>Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -8848,6 +10664,11 @@
           <t>High Pressure Filter Assembly 0077340521100000</t>
         </is>
       </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -8869,6 +10690,11 @@
           <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -8890,6 +10716,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -8911,6 +10742,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -8932,6 +10768,11 @@
           <t>Lower Leveling Cylinder CBV Assembly 00773405212800000</t>
         </is>
       </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -8953,6 +10794,11 @@
           <t>Lower Leveling Cylinder CBV Assembly 00773405212800000; Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -8974,6 +10820,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -8995,6 +10846,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -9016,6 +10872,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -9037,6 +10898,11 @@
           <t>Steering Priority Valve Assembly 00773405215000000; Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -9058,6 +10924,11 @@
           <t>Main Valve Assembly 00773405251600000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
         </is>
       </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -9079,6 +10950,11 @@
           <t>Lower Leveling Cylinder CBV Assembly 00773405212800000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
         </is>
       </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -9100,6 +10976,11 @@
           <t>Steering Priority Valve Assembly 00773405215000000; Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -9121,6 +11002,11 @@
           <t>Upper Leveling Cylinder CBV Assembly 00773405213000000</t>
         </is>
       </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -9142,6 +11028,11 @@
           <t>Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -9163,6 +11054,11 @@
           <t>Jib Cylinder CBV Assembly 00773405213200000</t>
         </is>
       </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -9184,6 +11080,11 @@
           <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -9205,6 +11106,11 @@
           <t>Steering Priority Valve Assembly 00773405215000000</t>
         </is>
       </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -9226,6 +11132,11 @@
           <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -9247,6 +11158,11 @@
           <t>Chassis 00773402830000000</t>
         </is>
       </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -9266,6 +11182,11 @@
       <c r="E394" t="inlineStr">
         <is>
           <t>Chassis 00773402830000000</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>ZA14JE-Li</t>
         </is>
       </c>
     </row>

--- a/Zoomlion/ZA14JE.xlsx
+++ b/Zoomlion/ZA14JE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F394"/>
+  <dimension ref="A1:F377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Material No.</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Item and Spec</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
@@ -2829,21 +2817,21 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>00773400700001020</t>
+          <t>00773400820001010</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hose holder</t>
+          <t>Lock pin</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -2855,7 +2843,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>00773400700001030</t>
+          <t>00773400820001020</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -2863,13 +2851,13 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nylon block</t>
+          <t>Electric control cabinet seat</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -2881,7 +2869,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>00773400700001040</t>
+          <t>00773400820001030</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -2889,13 +2877,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tube slot</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Rotary limit switch</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>GB/T96.1</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -2907,7 +2899,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>00773400700001050</t>
+          <t>00773400820001040</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -2915,13 +2907,13 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bending plate</t>
+          <t>Cushion pad</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -2933,21 +2925,21 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>00773400700001060</t>
+          <t>00773400820001070</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pipe-jacking</t>
+          <t>Axle I</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -2959,21 +2951,21 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>00773400700001080</t>
+          <t>00773400820001080</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chain mechanism</t>
+          <t>Axle II</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -2985,21 +2977,21 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>00773400700400000</t>
+          <t>00773400820001090</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tray</t>
+          <t>Adjusting pad</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3011,7 +3003,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>00773400710001010</t>
+          <t>00773400820001100</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -3019,13 +3011,13 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Rectangle tube</t>
+          <t>Front plate</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3037,15 +3029,15 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>00773400820001010</t>
+          <t>00773400820001120</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lock pin</t>
+          <t>Bending plate</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -3063,15 +3055,15 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>00773400820001020</t>
+          <t>00773400820001130</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Electric control cabinet seat</t>
+          <t>Gasket</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3089,7 +3081,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>00773400820001030</t>
+          <t>00773400820200000</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -3097,14 +3089,10 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Rotary limit switch</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>GB/T96.1</t>
-        </is>
-      </c>
+          <t>Turntable structure</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>Turntable 00773400820000000</t>
@@ -3119,15 +3107,15 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>00773400820001040</t>
+          <t>00773400820600000</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cushion pad</t>
+          <t>Slip ring cover</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3145,7 +3133,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>00773400820001070</t>
+          <t>00773400820800000</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -3153,7 +3141,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Axle I</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -3171,7 +3159,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>00773400820001080</t>
+          <t>00773400821000000</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -3179,7 +3167,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Axle II</t>
+          <t>Door stop mounting I</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -3197,15 +3185,15 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>00773400820001090</t>
+          <t>00773400821200000</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Adjusting pad</t>
+          <t>Door stop mounting II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -3223,7 +3211,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>00773400820001100</t>
+          <t>00773400821800000</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -3231,7 +3219,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Front plate</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -3249,21 +3237,21 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>00773400820001120</t>
+          <t>00773401010001010</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bending plate</t>
+          <t>Counterweight block</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Counterweight 00773401010000000</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3275,21 +3263,21 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>00773400820001130</t>
+          <t>00773401110001010</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Gasket</t>
+          <t>Lock seat</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3301,7 +3289,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>00773400820200000</t>
+          <t>00773401110001030</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3309,13 +3297,13 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turntable structure</t>
+          <t>Lock seat</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3327,7 +3315,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>00773400820600000</t>
+          <t>00773401110200000</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3335,13 +3323,13 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Slip ring cover</t>
+          <t>Lock seat</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -3353,21 +3341,21 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>00773400820800000</t>
+          <t>00773401110400000</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Lock seat</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3379,21 +3367,21 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>00773400821000000</t>
+          <t>00773401110600000</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Door stop mounting I</t>
+          <t>Hood weldment</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -3405,21 +3393,21 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>00773400821200000</t>
+          <t>00773401110800000</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Door stop mounting II</t>
+          <t>Hood weldment</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -3431,21 +3419,21 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>00773400821800000</t>
+          <t>00773402800001110</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>Gasket- steering knuckle</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -3457,21 +3445,21 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>00773401010001010</t>
+          <t>00773402800001260</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Counterweight block</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Counterweight 00773401010000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -3483,21 +3471,21 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>00773401110001010</t>
+          <t>00773402800001270</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Lock seat</t>
+          <t>Washer- steering knuckle pin</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -3509,7 +3497,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>00773401110001030</t>
+          <t>00773402820001020</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -3517,13 +3505,13 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Lock seat</t>
+          <t>Steering valve bracket</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -3535,21 +3523,21 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>00773401110200000</t>
+          <t>00773402820001030</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lock seat</t>
+          <t>Steering pull rod gasket</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -3561,7 +3549,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>00773401110400000</t>
+          <t>00773402820001050</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -3569,13 +3557,13 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lock seat</t>
+          <t>Motor bracket</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -3587,21 +3575,21 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>00773401110600000</t>
+          <t>00773402820001060</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hood weldment</t>
+          <t>Angle sensor protective hood</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -3613,21 +3601,21 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>00773401110800000</t>
+          <t>00773402820001070</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hood weldment</t>
+          <t>Main pin- steering knuckle</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -3639,15 +3627,15 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>00773402800001110</t>
+          <t>00773402820001080</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Gasket- steering knuckle</t>
+          <t>Steering pin</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -3665,15 +3653,15 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>00773402800001260</t>
+          <t>00773402820001090</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Charging port- protective box</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -3691,15 +3679,15 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>00773402800001270</t>
+          <t>00773402820001100</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washer- steering knuckle pin</t>
+          <t>Steering pin II</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -3717,15 +3705,15 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>00773402820001020</t>
+          <t>00773402820001110</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Steering valve bracket</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -3743,15 +3731,15 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>00773402820001030</t>
+          <t>00773402820001120</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Steering pull rod gasket</t>
+          <t>Spacer bush</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -3769,7 +3757,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>00773402820001050</t>
+          <t>00773402820001130</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -3777,7 +3765,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Motor bracket</t>
+          <t>Front cover</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -3795,15 +3783,15 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>00773402820001060</t>
+          <t>00773402820001140</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Angle sensor protective hood</t>
+          <t>Rear cover</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -3821,7 +3809,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>00773402820001070</t>
+          <t>00773402820001160</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -3829,7 +3817,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Main pin- steering knuckle</t>
+          <t>Rear tank- lower cover</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -3847,15 +3835,15 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>00773402820001080</t>
+          <t>00773402820400000</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Steering pin</t>
+          <t>Frame welds</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -3873,7 +3861,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>00773402820001090</t>
+          <t>00773402820600000</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -3881,7 +3869,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Charging port- protective box</t>
+          <t>Hub assembly- left steering knuckle</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -3899,7 +3887,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>00773402820001100</t>
+          <t>00773402820800000</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -3907,7 +3895,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Steering pin II</t>
+          <t>Hub assembly- right steering knuckle</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -3925,15 +3913,15 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>00773402820001110</t>
+          <t>00773402821020000</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Battery package cover</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -3951,15 +3939,15 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>00773402820001120</t>
+          <t>00773402821800000</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spacer bush</t>
+          <t>Steering cylinder</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -3977,15 +3965,15 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>00773402820001130</t>
+          <t>00773402822000000</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Front cover</t>
+          <t>Steering pull rod I</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -4003,7 +3991,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>00773402820001140</t>
+          <t>00773402822400000</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -4011,7 +3999,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Rear cover</t>
+          <t>Centre revolving joint- bracket welds</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -4029,15 +4017,15 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>00773402820001160</t>
+          <t>00773402830001120</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Rear tank- lower cover</t>
+          <t>Chassis counterweight II</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -4055,15 +4043,15 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>00773402820400000</t>
+          <t>00773402831001012</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Frame welds</t>
+          <t>Li-ion battery counterweight</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -4081,7 +4069,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>00773402820600000</t>
+          <t>00773402831030000</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -4089,7 +4077,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hub assembly- left steering knuckle</t>
+          <t>Battery package welds</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -4107,7 +4095,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>00773402820800000</t>
+          <t>00773405210210000</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -4115,13 +4103,13 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Hub assembly- right steering knuckle</t>
+          <t>Fuel tank</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -4133,21 +4121,21 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>00773402821020000</t>
+          <t>00773405210220000</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Battery package cover</t>
+          <t>Window cover</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -4159,7 +4147,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>00773402821800000</t>
+          <t>00773405210230000</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -4167,13 +4155,13 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Steering cylinder</t>
+          <t>Sealing plate</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -4185,21 +4173,21 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>00773402822000000</t>
+          <t>00773406 10000</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Steering pull rod I</t>
+          <t>Platform electrical control box assembly</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -4211,7 +4199,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>00773402822400000</t>
+          <t>00773406230450060</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -4219,13 +4207,13 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Centre revolving joint- bracket welds</t>
+          <t>Functional pump- driver B+ to functional pump A2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -4237,7 +4225,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>00773402830001120</t>
+          <t>00773406230450070</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -4245,13 +4233,13 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chassis counterweight II</t>
+          <t>Functional pump- driver M to functional pump D2</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -4263,21 +4251,21 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>00773402831001012</t>
+          <t>00773406230450090</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Li-ion battery counterweight</t>
+          <t>Functional pump-D1 to 与 A1 wiring</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -4289,7 +4277,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>00773402831030000</t>
+          <t>00773406230450100</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -4297,13 +4285,13 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Battery package welds</t>
+          <t>Battery positive pole to manual switch wiring</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -4315,7 +4303,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>00773405210210000</t>
+          <t>00773406230450110</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -4323,13 +4311,13 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Fuel tank</t>
+          <t>Manual switch to wire spool positive pole wiring</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -4341,7 +4329,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>00773405210220000</t>
+          <t>00773406230450120</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -4349,13 +4337,13 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Window cover</t>
+          <t>Battery negative pole to wire spool negative pole</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -4367,7 +4355,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>00773405210230000</t>
+          <t>00773406230450130</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -4375,13 +4363,13 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Sealing plate</t>
+          <t>Left spool B﹢  to brake IN</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -4393,7 +4381,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>00773406 10000</t>
+          <t>00773406230450140</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -4401,13 +4389,13 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Platform electrical control box assembly</t>
+          <t>Brake OUT to spool B﹢-right wiring</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -4419,7 +4407,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>00773406230450060</t>
+          <t>00773406230450150</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -4427,7 +4415,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Functional pump- driver B+ to functional pump A2</t>
+          <t>Spool B﹣  to brake negative pole</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -4445,7 +4433,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>00773406230450070</t>
+          <t>00773406230450160</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -4453,7 +4441,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Functional pump- driver M to functional pump D2</t>
+          <t>Emergency battery positive pole to auxiliary pump positive pump</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -4471,7 +4459,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>00773406230450090</t>
+          <t>00773406230450170</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -4479,7 +4467,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Functional pump-D1 to 与 A1 wiring</t>
+          <t>Emergency pump negative pole to auxiliary pump negative pole</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -4497,21 +4485,21 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>00773406230450100</t>
+          <t>00773406300201010</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Battery positive pole to manual switch wiring</t>
+          <t>Spacer</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Power System Assembly 00773406250450000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -4523,21 +4511,21 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>00773406230450110</t>
+          <t>00773700302800000</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Manual switch to wire spool positive pole wiring</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Power System Assembly 00773406250450000</t>
+          <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -4549,21 +4537,21 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>00773406230450120</t>
+          <t>00773700810001050</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Battery negative pole to wire spool negative pole</t>
+          <t>Shelves</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Power System Assembly 00773406250450000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -4575,7 +4563,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>00773406230450130</t>
+          <t>00773700810801010</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -4583,13 +4571,13 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Left spool B﹢  to brake IN</t>
+          <t>Handle sleeve</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Power System Assembly 00773406250450000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -4601,7 +4589,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>00773406230450140</t>
+          <t>00773700810801020</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -4609,13 +4597,13 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Brake OUT to spool B﹢-right wiring</t>
+          <t>Rod</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Power System Assembly 00773406250450000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -4627,7 +4615,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>00773406230450150</t>
+          <t>1010002078</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -4635,13 +4623,13 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spool B﹣  to brake negative pole</t>
+          <t>Gear pump</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Power System Assembly 00773406250450000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -4653,7 +4641,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>00773406230450160</t>
+          <t>1010002361</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -4661,13 +4649,13 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Emergency battery positive pole to auxiliary pump positive pump</t>
+          <t>Emergency pump</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Power System Assembly 00773406250450000</t>
+          <t>Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -4679,7 +4667,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>00773406230450170</t>
+          <t>1010201471</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -4687,13 +4675,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Emergency pump negative pole to auxiliary pump negative pole</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Rotary actuator</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>L20-08-180</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Power System Assembly 00773406250450000</t>
+          <t>Jib 00773400210000000</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -4705,21 +4697,21 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>00773406300201010</t>
+          <t>1010300748</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spacer</t>
+          <t>Non return valve</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -4731,21 +4723,21 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>00773700302800000</t>
+          <t>1010302829</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Non return valve</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773400310000000</t>
+          <t>Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -4757,21 +4749,21 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>00773700810001050</t>
+          <t>1010306016</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Shelves</t>
+          <t>Platform select-valve</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Telescopic Select-valve Assembly 00773405212400000</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -4783,21 +4775,21 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>00773700810801010</t>
+          <t>1010306020</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Handle sleeve</t>
+          <t>CBV</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Upper Leveling Cylinder CBV Assembly 00773405213000000; Jib Cylinder CBV Assembly 00773405213200000</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -4809,7 +4801,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>00773700810801020</t>
+          <t>1010306060</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -4817,13 +4809,13 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Rod</t>
+          <t>Telescopic CBV</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Telescopic Cylinder CBV Assembly 00773405213800000</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -4835,7 +4827,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1010002078</t>
+          <t>1010306226</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -4843,13 +4835,13 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Gear pump</t>
+          <t>Direction valve</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
+          <t>Platform Select-valve Assembly 00773405211200000</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -4861,7 +4853,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1010002361</t>
+          <t>1010306368</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4869,13 +4861,13 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Emergency pump</t>
+          <t>Cylinder control valve</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Emergency Pump Assembly 00773405255200000</t>
+          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -4887,25 +4879,21 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1010201471</t>
+          <t>1010306616</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Rotary actuator</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>L20-08-180</t>
-        </is>
-      </c>
+          <t>Lifting CBV</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Jib 00773400210000000</t>
+          <t>Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -4917,7 +4905,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1010300748</t>
+          <t>1010307351</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -4925,13 +4913,13 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Non return valve</t>
+          <t>Steering Priority Valve</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
+          <t>Steering Priority Valve Assembly 00773405215000000</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -4943,7 +4931,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1010302829</t>
+          <t>1010308361</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -4951,7 +4939,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Non return valve</t>
+          <t>Main valve</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -4969,7 +4957,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1010306016</t>
+          <t>1010601138</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4977,13 +4965,13 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Platform select-valve</t>
+          <t>High pressure filter</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Telescopic Select-valve Assembly 00773405212400000</t>
+          <t>High Pressure Filter Assembly 0077340521100000</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -4995,21 +4983,21 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1010306020</t>
+          <t>1010601202</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CBV</t>
+          <t>Return-oil filter</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Upper Leveling Cylinder CBV Assembly 00773405213000000; Jib Cylinder CBV Assembly 00773405213200000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -5021,7 +5009,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1010306060</t>
+          <t>1011200181</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -5029,13 +5017,13 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Telescopic CBV</t>
+          <t>Central revolving joint</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Telescopic Cylinder CBV Assembly 00773405213800000</t>
+          <t>Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -5047,7 +5035,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1010306226</t>
+          <t>1019807649</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -5055,7 +5043,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Direction valve</t>
+          <t>Check valve</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -5073,21 +5061,21 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1010306368</t>
+          <t>1019900975</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Cylinder control valve</t>
+          <t>Plug</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000</t>
+          <t>Main Valve Assembly 00773405251600000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -5099,21 +5087,21 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1010306616</t>
+          <t>1019901470</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Lifting CBV</t>
+          <t>Liquid level indicator</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -5125,7 +5113,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1010307351</t>
+          <t>1020005380</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -5133,13 +5121,13 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Steering Priority Valve</t>
+          <t>DC motor</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Steering Priority Valve Assembly 00773405215000000</t>
+          <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -5151,7 +5139,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1010308361</t>
+          <t>1020103232</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -5159,13 +5147,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Main valve</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>sheath</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Break</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Main Valve Assembly 00773405251600000</t>
+          <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -5177,21 +5169,21 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1010601138</t>
+          <t>1020103903</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>High pressure filter</t>
+          <t>Controller; controller</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>High Pressure Filter Assembly 0077340521100000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -5203,21 +5195,21 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1010601202</t>
+          <t>1020103955</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Return-oil filter</t>
+          <t>Connectors</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -5229,7 +5221,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1011200181</t>
+          <t>1020201651</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -5237,13 +5229,13 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Central revolving joint</t>
+          <t>Display</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Central Revolving Joint Assembly 00773405210800000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -5255,7 +5247,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1019807649</t>
+          <t>1020304559</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -5263,13 +5255,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Check valve</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Relay</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Light relay</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Platform Select-valve Assembly 00773405211200000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -5281,21 +5277,21 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1019900975</t>
+          <t>1020304584</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Plug</t>
+          <t>Power relay</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Main Valve Assembly 00773405251600000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -5307,21 +5303,21 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1019901470</t>
+          <t>1020304982</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Liquid level indicator</t>
+          <t>Alarm buzzer</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -5333,21 +5329,21 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1020005380</t>
+          <t>1020404399</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>1</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>DC motor</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Work alarm light</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Power System Assembly 00773406250450000</t>
+          <t>Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -5359,7 +5355,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1020103232</t>
+          <t>1020404405</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -5367,17 +5363,13 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>sheath</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
+          <t>Flashing buzzer</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Chassis Electric Cables 00773406230420000</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -5389,21 +5381,21 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1020103903</t>
+          <t>1020405061</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Controller; controller</t>
+          <t>Indicator panel</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -5415,7 +5407,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1020103955</t>
+          <t>1020509007</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -5423,7 +5415,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Connectors</t>
+          <t>Button seat</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -5441,21 +5433,21 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1020201651</t>
+          <t>1020516032</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>Limit switch (outside)- steering angle; Limit switch (inside)- steering angle; Boom length limit switch 1; Boom length limit switch 2</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
+          <t>Turntable Electric Cables 00773406230230011; Boom Electric Cables 00773406230230031</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -5467,25 +5459,25 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1020304559</t>
+          <t>1020519658</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Relay</t>
+          <t>Emergency button</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Light relay</t>
+          <t>Emergency stop switch</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -5497,7 +5489,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1020304584</t>
+          <t>1020520083</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -5505,13 +5497,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Power relay</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Toggle switch</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Driving orienteering</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -5523,21 +5519,25 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1020304982</t>
+          <t>1020520084</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Alarm buzzer</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>Toggle switch</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Platform rotating; Platform leveling; Jib lifting; Boom telescoping; Boom lifting; Tower boom lifting; Turntable rotary; Emergency power and enables; Platform rotary switch; Jib lifting switch; Jib telescoping</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -5549,21 +5549,25 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1020404399</t>
+          <t>1020520135</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0</v>
-      </c>
-      <c r="C197" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Toggle switch</t>
+        </is>
+      </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Work alarm light</t>
+          <t>Travel speed control; Platform leveling control</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -5575,7 +5579,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1020404405</t>
+          <t>1020520136</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -5583,10 +5587,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Flashing buzzer</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>Toggle switch</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>Platform Electrical Control Box Assembly 00773406230210000</t>
@@ -5601,7 +5609,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1020405061</t>
+          <t>1020520943</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -5609,13 +5617,13 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Indicator panel</t>
+          <t>Key switch</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -5627,21 +5635,21 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1020509007</t>
+          <t>1020520993</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Button seat</t>
+          <t>Joystick</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -5653,21 +5661,21 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1020516032</t>
+          <t>1020520994</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Limit switch (outside)- steering angle; Limit switch (inside)- steering angle; Boom length limit switch 1; Boom length limit switch 2</t>
+          <t>Joystick</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011; Boom Electric Cables 00773406230230031</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -5679,25 +5687,21 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1020519658</t>
+          <t>1020520995</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Emergency button</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Emergency stop switch</t>
-        </is>
-      </c>
+          <t>Potentiometer</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -5709,25 +5713,21 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1020520083</t>
+          <t>1020521022</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Toggle switch</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Driving orienteering</t>
-        </is>
-      </c>
+          <t>Foot switch; Footswitch</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Work Platform 00773400120000000; Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -5739,25 +5739,21 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1020520084</t>
+          <t>1020604934</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Toggle switch</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Platform rotating; Platform leveling; Jib lifting; Boom telescoping; Boom lifting; Tower boom lifting; Turntable rotary; Emergency power and enables; Platform rotary switch; Jib lifting switch; Jib telescoping</t>
-        </is>
-      </c>
+          <t>Terminal blocks</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -5769,25 +5765,25 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1020520135</t>
+          <t>1020700440</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Toggle switch</t>
+          <t>sheath</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Travel speed control; Platform leveling control</t>
+          <t>Plug-in slip ring 2; Negative or positive of power source</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Turntable Electric Cables 00773406230230011; Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -5799,7 +5795,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1020520136</t>
+          <t>1020700540</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -5807,17 +5803,13 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Toggle switch</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+          <t>Terminal resistance</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Boom Electric Cables 00773406230230031</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -5829,21 +5821,25 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1020520943</t>
+          <t>1020700942</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Key switch</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
+          <t>sheath</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Plug-in</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
+          <t>Turntable Electric Cables 00773406230230011; Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -5855,21 +5851,25 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1020520993</t>
+          <t>1020700951</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Joystick</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
+          <t>Speed control valve- tower boom lowering; Telescopic leveling selection valve; Speed control valve- main boom lowering; sheath</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Reversing valve 1- Jib rotary; Turntable right-turn valve; Reversing valve 2- expanding and leveling; Turntable left-turn valve; Reversing valve 1- expanding and leveling; Lifting valve-main boom; Lifting valve-tower boom; Work light; Charger; Jib lifting selection valve</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Turntable Electric Cables 00773406230230011; Boom Electric Cables 00773406230230031; Chassis Electric Cables 00773406230420000; Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -5881,7 +5881,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1020520994</t>
+          <t>1020700953</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -5889,13 +5889,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Joystick</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>sheath</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Charger communication</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -5907,7 +5911,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1020520995</t>
+          <t>1020700955</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -5915,13 +5919,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Potentiometer</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
+          <t>sheath</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Anti-extrusion switch</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -5933,21 +5941,25 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1020521022</t>
+          <t>1020700957</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Foot switch; Footswitch</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr"/>
+          <t>sheath; B﹢</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Plug-in; 48V socket</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
+          <t>Turntable Electric Cables 00773406230230011; Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -5959,21 +5971,21 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1020604934</t>
+          <t>1020702062</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Terminal blocks</t>
+          <t>Li-ion battery communication</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
+          <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -5985,11 +5997,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1020700440</t>
+          <t>1020703391</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -5998,7 +6010,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Plug-in slip ring 2; Negative or positive of power source</t>
+          <t>Plug-in slip ring 1</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -6015,7 +6027,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1020700540</t>
+          <t>1020703393</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -6023,13 +6035,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Terminal resistance</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
+          <t>Round plug connector</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Platform Electric Cables</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Boom Electric Cables 00773406230230031</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -6041,25 +6057,25 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1020700942</t>
+          <t>1020703394</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>sheath</t>
+          <t>Deutsch connector; Limit switch- tower boom stowed 1; Limit switch- tower boom stowed 2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Plug-in</t>
+          <t>Chain electric cables; Boom Electric Cables; Lift switch-tower boom lifting</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011; Chassis Electric Cables 00773406230420000</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000; Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -6071,25 +6087,21 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1020700951</t>
+          <t>1020704265</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>/; Speed control valve- tower boom lowering; Telescopic leveling selection valve; Speed control valve- main boom lowering; sheath</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Reversing valve 1- Jib rotary; Turntable right-turn valve; Reversing valve 2- expanding and leveling; Turntable left-turn valve; Reversing valve 1- expanding and leveling; Lifting valve-main boom; Lifting valve-tower boom; Work light; Charger; Jib lifting selection valve</t>
-        </is>
-      </c>
+          <t>Grounding terminal board</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011; Boom Electric Cables 00773406230230031; Chassis Electric Cables 00773406230420000; Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -6101,25 +6113,21 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1020700953</t>
+          <t>1020705826</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>sheath</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Charger communication</t>
-        </is>
-      </c>
+          <t>Diode terminal</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Chassis Electric Cables 00773406230420000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -6131,7 +6139,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1020700955</t>
+          <t>1020706505</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -6139,17 +6147,17 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>sheath</t>
+          <t>Plug connector</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Anti-extrusion switch</t>
+          <t>Chain cables</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
+          <t>Boom Electric Cables 00773406230230031</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -6161,25 +6169,21 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1020700957</t>
+          <t>1021404016</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>sheath; B﹢</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Plug-in; 48V socket</t>
-        </is>
-      </c>
+          <t>Load cell</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011; Chassis Electric Cables 00773406230420000</t>
+          <t>Work Platform 00773400120000000; Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -6191,7 +6195,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1020702062</t>
+          <t>1021404018</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -6199,7 +6203,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Li-ion battery communication</t>
+          <t>12V socket</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -6217,7 +6221,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1020703391</t>
+          <t>1021404019</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -6225,17 +6229,17 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>sheath</t>
+          <t>Boom angle sensor; sheath</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Plug-in slip ring 1</t>
+          <t>Frame angle sensor</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011; Chassis Electric Cables 00773406230420000</t>
+          <t>Boom Electric Cables 00773406230230031; Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -6247,7 +6251,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1020703393</t>
+          <t>1022200446</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -6255,17 +6259,17 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Round plug connector</t>
+          <t>sheath</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Platform Electric Cables</t>
+          <t>Platform plug connector</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -6277,25 +6281,25 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1020703394</t>
+          <t>1022259178</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Deutsch connector; Limit switch- tower boom stowed 1; Limit switch- tower boom stowed 2</t>
+          <t>sheath</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Chain electric cables; Boom Electric Cables; Lift switch-tower boom lifting</t>
+          <t>Battery diagnosis</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000; Turntable Electric Cables 00773406230230011</t>
+          <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -6307,21 +6311,25 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1020704265</t>
+          <t>1022270089</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Grounding terminal board</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>Plug connector</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Turntable electric control box</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Boom Electric Cables 00773406230230031</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -6333,21 +6341,21 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1020705826</t>
+          <t>1022399012</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Diode terminal</t>
+          <t>Wiring duct</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -6359,25 +6367,25 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1020706505</t>
+          <t>1029900318</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Plug connector</t>
+          <t>sheath</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Chain cables</t>
+          <t>Left-turn valve; Right-turn valve</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Boom Electric Cables 00773406230230031</t>
+          <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -6389,21 +6397,25 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1021404016</t>
+          <t>1029900385</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Load cell</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>sheath</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Steering angle sensor</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
+          <t>Chassis Electric Cables 00773406230420000</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -6415,7 +6427,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1021404018</t>
+          <t>1029900667</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -6423,13 +6435,13 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>12V socket</t>
+          <t>Main power switch (rotary knob)</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Chassis Electric Cables 00773406230420000</t>
+          <t>Power System Assembly 00773406250450000</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -6441,7 +6453,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1021404019</t>
+          <t>1029902630</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -6449,17 +6461,13 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Boom angle sensor; sheath</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>Frame angle sensor</t>
-        </is>
-      </c>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Boom Electric Cables 00773406230230031; Chassis Electric Cables 00773406230420000</t>
+          <t>Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -6471,25 +6479,21 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1022200446</t>
+          <t>1029902632</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>sheath</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>Platform plug connector</t>
-        </is>
-      </c>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
+          <t>Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -6501,25 +6505,25 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1022259178</t>
+          <t>1029902634</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>sheath</t>
+          <t>32-core sheath</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Battery diagnosis</t>
+          <t>Boom Electric Cables; Turntable Electric Cables</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Chassis Electric Cables 00773406230420000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -6531,7 +6535,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1022270089</t>
+          <t>1029902635</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -6539,7 +6543,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Plug connector</t>
+          <t>sheath</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6549,7 +6553,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Boom Electric Cables 00773406230230031</t>
+          <t>Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -6561,7 +6565,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1022399012</t>
+          <t>1029903316</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -6569,13 +6573,17 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Wiring duct</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr"/>
+          <t>sheath</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Turntable electric control box</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Turntable Electric Cables 00773406230230011</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -6587,25 +6595,25 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1029900318</t>
+          <t>1029903317</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>sheath</t>
+          <t>48-core sheath</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Left-turn valve; Right-turn valve</t>
+          <t>Turntable Electric Cables</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Chassis Electric Cables 00773406230420000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -6617,11 +6625,11 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1029900385</t>
+          <t>1029903711</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -6630,12 +6638,12 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Steering angle sensor</t>
+          <t>Upper plug-in of chain; Lower plug-in of chain</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Chassis Electric Cables 00773406230420000</t>
+          <t>Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -6647,21 +6655,21 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1029900667</t>
+          <t>1029904980</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Main power switch (rotary knob)</t>
+          <t>Terminal blocks; Terminal</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Power System Assembly 00773406250450000</t>
+          <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -6673,11 +6681,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1029902630</t>
+          <t>1029905392</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -6687,7 +6695,7 @@
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011</t>
+          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -6699,21 +6707,21 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1029902632</t>
+          <t>1030202173</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Slewing reducer</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011</t>
+          <t>Slewing Mechanism 00773400900000000</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -6725,7 +6733,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1029902634</t>
+          <t>1030202344</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -6733,17 +6741,13 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>32-core sheath</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>Boom Electric Cables; Turntable Electric Cables</t>
-        </is>
-      </c>
+          <t>Reducer motor assembly</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -6755,25 +6759,21 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1029902635</t>
+          <t>1030800654</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>sheath</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>Turntable electric control box</t>
-        </is>
-      </c>
+          <t>Tire IN240/55D17.5</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -6785,25 +6785,25 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1029903316</t>
+          <t>1040000090</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>sheath</t>
+          <t>Bolt M10×30-8.8</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Turntable electric control box</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables 00773406230230011</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -6815,25 +6815,25 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1029903317</t>
+          <t>1040000698</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>48-core sheath</t>
+          <t>Bolt M16×90-10.9</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Turntable Electric Cables</t>
+          <t>GB/T1228</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001</t>
+          <t>Slewing Mechanism 00773400900000000</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -6845,25 +6845,25 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1029903711</t>
+          <t>1040001631</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>sheath</t>
+          <t>Bolt M6×20-A2-70; Bolt M6×20-8.8</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Upper plug-in of chain; Lower plug-in of chain</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Platform Electric Cables 00773406230440000 Chain Cables Change 00773406230610000</t>
+          <t>Work Platform 00773400120000000; Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -6875,21 +6875,25 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1029904980</t>
+          <t>1040002433</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Terminal blocks; Terminal</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
+          <t>Bolt M10×20-8.8</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>GB/T5783</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773406230220001; Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Upper Boom Assembly 00773400310000000; Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -6901,21 +6905,25 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1029905392</t>
+          <t>1040002434</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
+          <t>Bolt M10×25-8.8; Bolt</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>GB/T5783</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Platform Electrical Control Box Assembly 00773406230210000</t>
+          <t>Upper Boom Assembly 00773400310000000; Turntable 00773400820000000; Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -6927,21 +6935,25 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1030202173</t>
+          <t>1040002435</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Slewing reducer</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr"/>
+          <t>Bolt M10×35-8.8</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>GB/T5783</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Slewing Mechanism 00773400900000000</t>
+          <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -6953,21 +6965,25 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1030202344</t>
+          <t>1040002436</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Reducer motor assembly</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>Bolt M12×25-8.8</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>GB/T5783</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -6979,21 +6995,25 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1030800654</t>
+          <t>1040002437</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Tire IN240/55D17.5</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr"/>
+          <t>Bolt M12×35-8.8</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>GB/T5783</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Jib 00773400210000000</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -7005,15 +7025,15 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1040000090</t>
+          <t>1040002555</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Bolt M10×30-8.8</t>
+          <t>Bolt M6×16-70</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7023,7 +7043,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -7035,25 +7055,25 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1040000698</t>
+          <t>1040002738</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Bolt M16×90-10.9</t>
+          <t>Bolt M6×12-8.8</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>GB/T1228</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Slewing Mechanism 00773400900000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -7065,7 +7085,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1040001631</t>
+          <t>1040003252</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -7073,17 +7093,17 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Bolt M6×20-A2-70; Bolt M6×20-8.8</t>
+          <t>Hexagon socket head cap screw M8×20-12.9</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Turntable 00773400820000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -7095,15 +7115,15 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1040002433</t>
+          <t>1040003324</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Bolt M10×20-8.8</t>
+          <t>Bolt M16×30-10.9-DKL</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7113,7 +7133,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773400310000000; Tower Boom Assembly 00773400410000000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -7125,15 +7145,15 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1040002434</t>
+          <t>1040004033</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Bolt M10×25-8.8; Bolt</t>
+          <t>Bolt M10×25-10.9</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7143,7 +7163,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773400310000000; Turntable 00773400820000000; Hydraulic Pump Assembly 00773405250400000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -7155,7 +7175,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1040002435</t>
+          <t>1040004496</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -7163,7 +7183,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bolt M10×35-8.8</t>
+          <t>Bolt M16×45-10.9</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7173,7 +7193,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773400310000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -7185,15 +7205,15 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1040002436</t>
+          <t>1040004499</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Bolt M12×25-8.8</t>
+          <t>Bolt M20×45-8.8</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -7203,7 +7223,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -7215,15 +7235,15 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1040002437</t>
+          <t>1040004500</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bolt M12×35-8.8</t>
+          <t>Bolt M30×50-8.8</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7233,7 +7253,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Jib 00773400210000000</t>
+          <t>Counterweight 00773401010000000</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -7245,25 +7265,25 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1040002555</t>
+          <t>1040004505</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bolt M6×16-70</t>
+          <t>Bolt M24×280-10.9</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -7275,7 +7295,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1040002738</t>
+          <t>1040004509</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -7283,7 +7303,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bolt M6×12-8.8</t>
+          <t>Bolt M10×50-8.8</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7293,7 +7313,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -7305,25 +7325,25 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1040003252</t>
+          <t>1040004511</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Hexagon socket head cap screw M8×20-12.9</t>
+          <t>Bolt M12×30-8.8</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Upper Boom Assembly 00773400310000000; Turntable 00773400820000000; Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -7335,15 +7355,15 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1040003324</t>
+          <t>1040004517</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Bolt M16×30-10.9-DKL</t>
+          <t>Bolt M8×16-8.8; BoltM8×16-8.8</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7353,7 +7373,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Upper Boom Assembly 00773400310000000; Hood 00773401110000000; Hydraulic Tank Assembly 00773405210200000; Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -7365,15 +7385,15 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1040004033</t>
+          <t>1040004518</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Bolt M10×25-10.9</t>
+          <t>Bolt M8×20-8.8; BoltM8×20-8.8</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7383,7 +7403,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Turntable 00773400820000000; Chassis 00773402830000000; Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -7395,15 +7415,15 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1040004496</t>
+          <t>1040004519</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bolt M16×45-10.9</t>
+          <t>Bolt M8×25-8.8</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7413,7 +7433,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -7425,15 +7445,15 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1040004499</t>
+          <t>1040004520</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Bolt M20×45-8.8</t>
+          <t>Bolt M8×30-8.8; Bolt</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -7443,7 +7463,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Turntable 00773400820000000; Chassis 00773402830000000; Steering Priority Valve Assembly 00773405215000000</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -7455,15 +7475,15 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1040004500</t>
+          <t>1040004521</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Bolt M30×50-8.8</t>
+          <t>BoltM8×45-8.8</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7473,7 +7493,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Counterweight 00773401010000000</t>
+          <t>Upper Leveling Cylinder CBV Assembly 00773405213000000</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -7485,25 +7505,25 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1040004505</t>
+          <t>1040004522</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Bolt M24×280-10.9</t>
+          <t>BoltM8×50-8.8</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -7515,25 +7535,25 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1040004509</t>
+          <t>1040004535</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Bolt M10×50-8.8</t>
+          <t>Bolt M10×60-8.8</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Jib 00773400210000000</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -7545,15 +7565,15 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1040004511</t>
+          <t>1040004553</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Bolt M12×30-8.8</t>
+          <t>Bolt M6×35-8.8</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7563,7 +7583,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773400310000000; Turntable 00773400820000000; Chassis 00773402830000000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -7575,25 +7595,25 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1040004517</t>
+          <t>1040004556</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Bolt M8×16-8.8; BoltM8×16-8.8</t>
+          <t>Bolt M12×35-8.8</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T16674.1</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773400310000000; Chain System 00773400710000000; Hood 00773401110000000; Hydraulic Tank Assembly 00773405210200000; Central Revolving Joint Assembly 00773405210800000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -7605,15 +7625,15 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1040004518</t>
+          <t>1040004565</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bolt M8×20-8.8; BoltM8×20-8.8</t>
+          <t>Bolt M10×30-8.8</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7623,7 +7643,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000; Chassis 00773402830000000; Main Valve Assembly 00773405251600000</t>
+          <t>Upper Boom Assembly 00773400310000000; Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -7635,15 +7655,15 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1040004519</t>
+          <t>1040004570</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bolt M8×25-8.8</t>
+          <t>Bolt M16×30-8.8</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7653,7 +7673,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000; Hood 00773401110000000</t>
+          <t>Tower Boom Assembly 00773400410000000; Turntable 00773400820000000; Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -7665,15 +7685,15 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1040004520</t>
+          <t>1040004590</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Bolt M8×30-8.8; Bolt</t>
+          <t>Bolt M8×14-8.8</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7683,7 +7703,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000; Chassis 00773402830000000; Steering Priority Valve Assembly 00773405215000000</t>
+          <t>Turntable 00773400820000000; Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -7695,7 +7715,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1040004521</t>
+          <t>1040004613</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -7703,17 +7723,17 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>BoltM8×45-8.8</t>
+          <t>Bolt M24×60-10.9</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Upper Leveling Cylinder CBV Assembly 00773405213000000</t>
+          <t>Counterweight 00773401010000000</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -7725,15 +7745,15 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1040004522</t>
+          <t>1040004619</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>BoltM8×50-8.8</t>
+          <t>Bolt M8×35-8.8</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7743,7 +7763,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -7755,25 +7775,25 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1040004535</t>
+          <t>1040004646</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Bolt M10×60-8.8</t>
+          <t>Bolt M10×15-8.8</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Jib 00773400210000000</t>
+          <t>Tower Boom Assembly 00773400410000000; Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -7785,25 +7805,25 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1040004553</t>
+          <t>1040004649</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bolt M6×35-8.8</t>
+          <t>Screw 5/8-11UNC×45-10.9</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>ANSIB18.3</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -7815,25 +7835,25 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1040004556</t>
+          <t>1040004653</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Bolt M12×35-8.8</t>
+          <t>Bolt M12×30-10.9</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>GB/T16674.1</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -7845,25 +7865,25 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1040004557</t>
+          <t>1040004654</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Bolt M8×50-8.8</t>
+          <t>Bolt M16×1.5×40-10.9</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>GB/T16674.1</t>
+          <t>GB/T5787</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -7875,25 +7895,25 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1040004565</t>
+          <t>1040004656</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Bolt M10×30-8.8</t>
+          <t>Bolt M10×65-8.8</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773400310000000; Hood 00773401110000000</t>
+          <t>Jib 00773400210000000</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -7905,25 +7925,25 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1040004570</t>
+          <t>1040004657</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Bolt M16×30-8.8</t>
+          <t>Bolt M12×80-8.8</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773400410000000; Turntable 00773400820000000; Chassis 00773402830000000</t>
+          <t>Jib 00773400210000000</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -7935,25 +7955,25 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1040004590</t>
+          <t>1040004658</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Bolt M8×14-8.8</t>
+          <t>Bolt M10×110-8.8</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000; Hood 00773401110000000</t>
+          <t>Jib 00773400210000000</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -7965,25 +7985,25 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1040004613</t>
+          <t>1040005831</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bolt M24×60-10.9</t>
+          <t>Bolt M10×25-DKL</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T5789</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Counterweight 00773401010000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -7995,25 +8015,25 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1040004619</t>
+          <t>1040005851</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bolt M8×35-8.8</t>
+          <t>Screw M10×25-8.8</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5787</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -8025,25 +8045,25 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1040004646</t>
+          <t>1040005888</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Bolt M10×15-8.8</t>
+          <t>Bolt M12×120-10.9</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773400410000000; Turntable 00773400820000000</t>
+          <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -8055,25 +8075,25 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1040004649</t>
+          <t>1040100069</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Screw 5/8-11UNC×45-10.9</t>
+          <t>Screw M8×20-8.8</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>ANSIB18.3</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>High Pressure Filter Assembly 0077340521100000</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -8085,7 +8105,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1040004653</t>
+          <t>1040100105</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -8093,17 +8113,17 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Bolt M12×30-10.9</t>
+          <t>Screw M6×25-8.8</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -8115,7 +8135,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1040004654</t>
+          <t>1040100148</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -8123,17 +8143,17 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Bolt M16×1.5×40-10.9</t>
+          <t>Screw M8×45-8.8</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>GB/T5787</t>
+          <t>GB/T5783; GB/T70.1</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Jib Cylinder CBV Assembly 00773405213200000; Telescopic Cylinder CBV Assembly 00773405213800000</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -8145,25 +8165,25 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1040004656</t>
+          <t>1040100714</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Bolt M10×65-8.8</t>
+          <t>Screw M12×130-8.8</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Jib 00773400210000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -8175,25 +8195,25 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1040004657</t>
+          <t>1040101492</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Bolt M12×80-8.8</t>
+          <t>Screw</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Jib 00773400210000000</t>
+          <t>Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -8205,7 +8225,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1040004658</t>
+          <t>1040101494</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -8213,17 +8233,17 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Bolt M10×110-8.8</t>
+          <t>Screw M12×40-8.8</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Jib 00773400210000000</t>
+          <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -8235,25 +8255,25 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1040004670</t>
+          <t>1040101846</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Bolt M5×60-8.8</t>
+          <t>Screw M4×10-8.8</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -8265,25 +8285,25 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1040005831</t>
+          <t>1040101995</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Bolt M10×25-DKL</t>
+          <t>Screw M10×30-8.8</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>GB/T5789</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -8295,25 +8315,25 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1040005851</t>
+          <t>1040102429</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Screw M10×25-8.8</t>
+          <t>Screw M4×8</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>GB/T5787</t>
+          <t>GB/T70.3</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -8325,25 +8345,25 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1040005888</t>
+          <t>1040102739</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Bolt M12×120-10.9</t>
+          <t>Screw M8×60-8.8</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773400410000000</t>
+          <t>Tower Boom Assembly 00773400410000000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -8355,15 +8375,15 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1040100069</t>
+          <t>1040102773</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Screw M8×20-8.8</t>
+          <t>Screw M6×40-8.8</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8373,7 +8393,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>High Pressure Filter Assembly 0077340521100000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -8385,25 +8405,25 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1040100105</t>
+          <t>1040102774</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Screw M6×25-8.8</t>
+          <t>Screw M6×15-8.8</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T70.1; GB/T97.1</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Work Platform 00773400120000000; Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -8415,25 +8435,25 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1040100148</t>
+          <t>1040102777</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Screw M8×45-8.8</t>
+          <t>Screw M4×50-8.8</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>GB/T5783; GB/T70.1</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Jib Cylinder CBV Assembly 00773405213200000; Telescopic Cylinder CBV Assembly 00773405213800000</t>
+          <t>Platform Select-valve Assembly 00773405211200000</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -8445,15 +8465,15 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1040100714</t>
+          <t>1040103038</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Screw M12×130-8.8</t>
+          <t>Screw M5×10</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8463,7 +8483,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -8475,15 +8495,15 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1040101492</t>
+          <t>1040103106</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Screw</t>
+          <t>Screw M5×30-8.8</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8493,7 +8513,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Emergency Pump Assembly 00773405255200000</t>
+          <t>Jib 00773400210000000</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -8505,7 +8525,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1040101494</t>
+          <t>1040103107</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -8513,7 +8533,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Screw M12×40-8.8</t>
+          <t>Screw M5×45-8.8</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8523,7 +8543,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773400410000000</t>
+          <t>Telescopic Select-valve Assembly 00773405212400000</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -8535,15 +8555,15 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1040101846</t>
+          <t>1040103112</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Screw M4×10-8.8</t>
+          <t>Screw M8×25-8.8</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8553,7 +8573,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -8565,7 +8585,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1040101995</t>
+          <t>1040103140</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -8573,7 +8593,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Screw M10×30-8.8</t>
+          <t>Screw M12×25-8.8</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8595,25 +8615,25 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1040102429</t>
+          <t>1040200113</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Screw M4×8</t>
+          <t>Nut M10-8</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>GB/T70.3</t>
+          <t>GB/T6170</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -8625,25 +8645,25 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1040102737</t>
+          <t>1040200161</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Screw M8×30-8.8</t>
+          <t>Nut M16-8</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T889</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -8655,25 +8675,25 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1040102739</t>
+          <t>1040200503</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Screw M8×60-8.8</t>
+          <t>Nut M8-8</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773400410000000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
+          <t>Turntable 00773400820000000; Hood 00773401110000000; Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -8685,25 +8705,25 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1040102773</t>
+          <t>1040200504</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Screw M6×40-8.8</t>
+          <t>Nut M10-8</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Work Platform 00773400120000000; Jib 00773400210000000</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -8715,7 +8735,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1040102774</t>
+          <t>1040200507</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -8723,17 +8743,17 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Screw M6×15-8.8</t>
+          <t>Nut M12-8</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>GB/T70.1; GB/T97.1</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Tower Boom Assembly 00773400410000000</t>
+          <t>Work Platform 00773400120000000; Jib 00773400210000000; Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -8745,25 +8765,25 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1040102777</t>
+          <t>1040201089</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Screw M4×50-8.8</t>
+          <t>Nut M8-8</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T6170</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Platform Select-valve Assembly 00773405211200000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -8775,25 +8795,25 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1040103038</t>
+          <t>1040201111</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Screw M5×10</t>
+          <t>Nut M24-10</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T889</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773400310000000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -8805,25 +8825,25 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1040103106</t>
+          <t>1040201772</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Screw M5×30-8.8</t>
+          <t>Nut M4-A2-70</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T6170</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Jib 00773400210000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -8835,25 +8855,25 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1040103107</t>
+          <t>1040201860</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Screw M5×45-8.8</t>
+          <t>Nut M10</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>QC/T608-2011</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Telescopic Select-valve Assembly 00773405212400000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -8865,20 +8885,20 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1040103112</t>
+          <t>1040201865</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Screw M8×25-8.8</t>
+          <t>Nut M6-8</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T6170</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -8895,25 +8915,25 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1040103140</t>
+          <t>1040201896</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Screw M12×25-8.8</t>
+          <t>Nut M6-8</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773400410000000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -8925,25 +8945,25 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1040200113</t>
+          <t>1040201902</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Nut M10-8</t>
+          <t>Nut M6-6</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>GB/T6170</t>
+          <t>GB/T802</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Work Platform 00773400120000000</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -8955,20 +8975,20 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1040200161</t>
+          <t>1040202280</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Nut M16-8</t>
+          <t>Nut M24-05-DKL</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>GB/T889</t>
+          <t>GB/T6181</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -8985,25 +9005,25 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1040200503</t>
+          <t>1040202296</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Nut M8-8</t>
+          <t>Nut 5/8-18UNF-10 (Spiralock)</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>ANSIB18.2.2</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000; Turntable 00773400820000000; Hood 00773401110000000; Chassis 00773402830000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -9015,25 +9035,25 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1040200504</t>
+          <t>1040300060</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Nut M10-8</t>
+          <t>Washer 5</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>GB/T93</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Jib 00773400210000000</t>
+          <t>Platform Select-valve Assembly 00773405211200000; Telescopic Select-valve Assembly 00773405212400000</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -9045,25 +9065,25 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1040200507</t>
+          <t>1040300186</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Nut M12-8</t>
+          <t>Gasket 16</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>GB/T1230</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Jib 00773400210000000; Tower Boom Assembly 00773400410000000</t>
+          <t>Slewing Mechanism 00773400900000000</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -9075,25 +9095,25 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1040200574</t>
+          <t>1040300735</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Nut M5-8</t>
+          <t>Gasket 6-200HV</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>GB/T6170</t>
+          <t>GB/T96.1</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Work Platform 00773400120000000; Turntable 00773400820000000</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -9105,25 +9125,25 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1040201089</t>
+          <t>1040300771</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Nut M8-8</t>
+          <t>Gasket 6-200HV</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>GB/T6170</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Work Platform 00773400120000000; Tower Boom Assembly 00773400410000000; Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -9135,25 +9155,25 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1040201111</t>
+          <t>1040301502</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Nut M24-10</t>
+          <t>Washer</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>GB/T889</t>
+          <t>GB/T93</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000; Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -9165,25 +9185,25 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1040201772</t>
+          <t>1040301510</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Nut M4-A2-70</t>
+          <t>Washer 8</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>GB/T6170</t>
+          <t>GB/T93</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>High Pressure Filter Assembly 0077340521100000; Lower Leveling Cylinder CBV Assembly 00773405212800000; Upper Leveling Cylinder CBV Assembly 00773405213000000; Jib Cylinder CBV Assembly 00773405213200000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000; Telescopic Cylinder CBV Assembly 00773405213800000</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -9195,20 +9215,20 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>1040201860</t>
+          <t>1040301511</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Nut M10</t>
+          <t>Washer 24-200HV</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>QC/T608-2011</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -9225,25 +9245,25 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1040201865</t>
+          <t>1040301513</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Nut M6-8</t>
+          <t>Gasket 30-200HV</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>GB/T6170</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Counterweight 00773401010000000</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -9255,25 +9275,25 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1040201896</t>
+          <t>1040301515</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Nut M6-8</t>
+          <t>Gasket 8-200HV; Washer 8-200HV; Washer 8; Washer</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>GB/T97.1; GB/T97.1-2002</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Work Platform 00773400120000000; Upper Boom Assembly 00773400310000000; Tower Boom Assembly 00773400410000000; Turntable 00773400820000000; Hood 00773401110000000; Chassis 00773402830000000; Hydraulic Tank Assembly 00773405210200000; Steering Priority Valve Assembly 00773405215000000; Central Revolving Joint Assembly 00773405210800000; High Pressure Filter Assembly 0077340521100000; Main Valve Assembly 00773405251600000; Jib Cylinder CBV Assembly 00773405213200000</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -9285,25 +9305,25 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1040201902</t>
+          <t>1040302480</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Nut M6-6</t>
+          <t>Gasket 8-200HV</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>GB/T802</t>
+          <t>GB/T96.1</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000</t>
+          <t>Turntable 00773400820000000; Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -9315,25 +9335,25 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1040202280</t>
+          <t>1040302483</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Nut M24-05-DKL</t>
+          <t>Gasket 24-200HV</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>GB/T6181</t>
+          <t>GB/T96.1</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Counterweight 00773401010000000</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -9345,25 +9365,25 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1040202296</t>
+          <t>1040302489</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Nut 5/8-18UNF-10 (Spiralock)</t>
+          <t>Gasket 10-200HV; Washer</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>ANSIB18.2.2</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Work Platform 00773400120000000; Jib 00773400210000000; Upper Boom Assembly 00773400310000000; Tower Boom Assembly 00773400410000000; Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -9375,7 +9395,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1040300060</t>
+          <t>1040302490</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -9383,17 +9403,17 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Washer 5</t>
+          <t>Washer 12-200HV</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>GB/T93</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Platform Select-valve Assembly 00773405211200000; Telescopic Select-valve Assembly 00773405212400000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -9405,25 +9425,25 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1040300186</t>
+          <t>1040302492</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Gasket 16</t>
+          <t>Gasket 16-200HV; Washer 16-200HV</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>GB/T1230</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Slewing Mechanism 00773400900000000</t>
+          <t>Work Platform 00773400120000000; Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -9435,25 +9455,25 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1040300735</t>
+          <t>1040302506</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Gasket 6-200HV</t>
+          <t>Check ring 32</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>GB/T96.1</t>
+          <t>JB/ZQ4342</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Turntable 00773400820000000</t>
+          <t>Upper Boom Assembly 00773400310000000</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -9465,25 +9485,25 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1040300771</t>
+          <t>1040302512</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Gasket 6-200HV</t>
+          <t>Gasket 10-200HV</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>GB/T97.1</t>
+          <t>GB/T96.1</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Tower Boom Assembly 00773400410000000; Hood 00773401110000000</t>
+          <t>Work Platform 00773400120000000; Turntable 00773400820000000; Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -9495,25 +9515,25 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1040301502</t>
+          <t>1040302817</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Washer</t>
+          <t>Washer 16-DKL</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>GB/T93</t>
+          <t>GB/T1230-1991</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Assembly 00773405250400000; Emergency Pump Assembly 00773405255200000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -9525,25 +9545,25 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1040301510</t>
+          <t>1040302821</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Gasket 8; Washer 8</t>
+          <t>Gasket 12-200HV; Washer 12</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>GB/T93</t>
+          <t>GB/T96.1</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000; High Pressure Filter Assembly 0077340521100000; Lower Leveling Cylinder CBV Assembly 00773405212800000; Upper Leveling Cylinder CBV Assembly 00773405213000000; Jib Cylinder CBV Assembly 00773405213200000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000; Telescopic Cylinder CBV Assembly 00773405213800000</t>
+          <t>Work Platform 00773400120000000; Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -9555,7 +9575,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1040301511</t>
+          <t>1040500394</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -9563,12 +9583,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Washer 24-200HV</t>
+          <t>Open pin 5×40</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>GB/T97.1</t>
+          <t>GB/T91</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -9585,25 +9605,21 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1040301513</t>
+          <t>1089900652</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Gasket 30-200HV</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>GB/T5783</t>
-        </is>
-      </c>
+          <t>Sealing strip</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Counterweight 00773401010000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -9615,25 +9631,21 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1040301515</t>
+          <t>1100700163</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Gasket 8-200HV; Washer 8-200HV; Washer 8; Washer</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>GB/T97.1; GB/T97.1-2002</t>
-        </is>
-      </c>
+          <t>Door knob</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Upper Boom Assembly 00773400310000000; Chain System 00773400710000000; Tower Boom Assembly 00773400410000000; Turntable 00773400820000000; Hood 00773401110000000; Chassis 00773402830000000; Hydraulic Tank Assembly 00773405210200000; Steering Priority Valve Assembly 00773405215000000; Central Revolving Joint Assembly 00773405210800000; High Pressure Filter Assembly 0077340521100000; Main Valve Assembly 00773405251600000; Jib Cylinder CBV Assembly 00773405213200000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -9645,25 +9657,21 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1040302480</t>
+          <t>1101000089</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Gasket 8-200HV</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>GB/T96.1</t>
-        </is>
-      </c>
+          <t>Hinge</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Turntable 00773400820000000; Hood 00773401110000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -9675,25 +9683,21 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1040302483</t>
+          <t>1101000164</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Gasket 24-200HV</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>GB/T96.1</t>
-        </is>
-      </c>
+          <t>Metal lock</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Counterweight 00773401010000000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -9705,25 +9709,21 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1040302489</t>
+          <t>1109900778</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Gasket 10-200HV; Washer</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>GB/T97.1</t>
-        </is>
-      </c>
+          <t>Door lock</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Jib 00773400210000000; Upper Boom Assembly 00773400310000000; Tower Boom Assembly 00773400410000000; Emergency Pump Assembly 00773405255200000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -9735,25 +9735,21 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1040302490</t>
+          <t>1109900779</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Washer 12-200HV</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>GB/T97.1</t>
-        </is>
-      </c>
+          <t>Door lock</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -9765,25 +9761,21 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1040302492</t>
+          <t>1110100355</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Gasket 16-200HV; Washer 16-200HV</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>GB/T97.1</t>
-        </is>
-      </c>
+          <t>Gas spring</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Chassis 00773402830000000</t>
+          <t>Hood 00773401110000000</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -9795,25 +9787,21 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1040302506</t>
+          <t>1140101461</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Check ring 32</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>JB/ZQ4342</t>
-        </is>
-      </c>
+          <t>Male stud connector</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773400310000000</t>
+          <t>Steering Priority Valve Assembly 00773405215000000; Platform Select-valve Assembly 00773405211200000; Telescopic Select-valve Assembly 00773405212400000</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -9825,25 +9813,21 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1040302512</t>
+          <t>1140101463</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Gasket 10-200HV</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>GB/T96.1</t>
-        </is>
-      </c>
+          <t>Male stud connector</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Turntable 00773400820000000; Hood 00773401110000000</t>
+          <t>Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -9855,25 +9839,21 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1040302817</t>
+          <t>1140101465</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Washer 16-DKL</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>GB/T1230-1991</t>
-        </is>
-      </c>
+          <t>Male stud connector</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Steering Priority Valve Assembly 00773405215000000; Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -9885,25 +9865,21 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1040302821</t>
+          <t>1140101466</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Gasket 12-200HV; Washer 12</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>GB/T96.1</t>
-        </is>
-      </c>
+          <t>Male stud connector</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Work Platform 00773400120000000; Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -9915,25 +9891,21 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1040500394</t>
+          <t>1140101476</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Open pin 5×40</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>GB/T91</t>
-        </is>
-      </c>
+          <t>Tube to swivel</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000; Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -9945,21 +9917,21 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1089900652</t>
+          <t>1140101477</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Sealing strip</t>
+          <t>Tube to swivel</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000; Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -9971,21 +9943,21 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1100700163</t>
+          <t>1140101478</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Door knob</t>
+          <t>Tube to swivel</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -9997,21 +9969,21 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1101000089</t>
+          <t>1140101483</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>T-junction</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -10023,7 +9995,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1101000164</t>
+          <t>1140101484</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -10031,13 +10003,13 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Metal lock</t>
+          <t>T-junction</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Chassis 00773402830000000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000; Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -10049,7 +10021,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1109900778</t>
+          <t>1140101485</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -10057,13 +10029,13 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>T-junction</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -10075,7 +10047,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1109900779</t>
+          <t>1140101628</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -10083,13 +10055,13 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Door lock</t>
+          <t>Plug screw</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -10101,21 +10073,21 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1109900992</t>
+          <t>1140101629</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Cable cross-bar 27000.12</t>
+          <t>Plug screw</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -10127,21 +10099,21 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1109900994</t>
+          <t>1140101827</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Cable shim 35.1</t>
+          <t>Build-up joint</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -10153,21 +10125,21 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1109900996</t>
+          <t>1140102936</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>links section body 2700.12.075.0</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Telescopic Cylinder CBV Assembly 00773405213800000</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -10179,7 +10151,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1109900997</t>
+          <t>1140103405</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -10187,13 +10159,13 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Connector link hole 26101.12.C.1</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -10205,21 +10177,21 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1109900998</t>
+          <t>1140107481</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Connector link pin 26101.12.C.2</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Chain System 00773400710000000</t>
+          <t>High Pressure Filter Assembly 0077340521100000</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -10231,21 +10203,21 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1110100355</t>
+          <t>1140107825</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Gas spring</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Hood 00773401110000000</t>
+          <t>Hydraulic Tank Assembly 00773405210200000</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -10257,21 +10229,21 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1140101461</t>
+          <t>1140111252</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>Reducer union</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Steering Priority Valve Assembly 00773405215000000; Platform Select-valve Assembly 00773405211200000; Telescopic Select-valve Assembly 00773405212400000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -10283,7 +10255,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1140101463</t>
+          <t>1140111483</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -10291,13 +10263,13 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>Reducer union</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Main Valve Assembly 00773405251600000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -10309,11 +10281,11 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1140101465</t>
+          <t>1140112820</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -10323,7 +10295,7 @@
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Steering Priority Valve Assembly 00773405215000000; Central Revolving Joint Assembly 00773405210800000</t>
+          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -10335,11 +10307,11 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1140101466</t>
+          <t>1140112827</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -10349,7 +10321,7 @@
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000; Emergency Pump Assembly 00773405255200000</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -10361,21 +10333,21 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1140101476</t>
+          <t>1140113796</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Build-up joint</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000; Emergency Pump Assembly 00773405255200000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -10387,21 +10359,21 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1140101477</t>
+          <t>1140114034</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Hydraulic pipe joint</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Assembly 00773405250400000; Emergency Pump Assembly 00773405255200000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -10413,7 +10385,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1140101478</t>
+          <t>1140114035</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -10421,13 +10393,13 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Hydraulic pipe joint</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Central Revolving Joint Assembly 00773405210800000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -10439,21 +10411,21 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1140101483</t>
+          <t>1140114036</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>T-junction</t>
+          <t>Hydraulic pipe joint; Male stud connector</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
+          <t>Steering Priority Valve Assembly 00773405215000000; Central Revolving Joint Assembly 00773405210800000</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -10465,21 +10437,21 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1140101484</t>
+          <t>1140114040</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>T-junction</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000; Central Revolving Joint Assembly 00773405210800000</t>
+          <t>Main Valve Assembly 00773405251600000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -10491,11 +10463,11 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1140101485</t>
+          <t>1140114046</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -10505,7 +10477,7 @@
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
+          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -10517,21 +10489,21 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1140101628</t>
+          <t>1140114187</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Plug screw</t>
+          <t>Test joint</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Steering Priority Valve Assembly 00773405215000000; Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -10543,7 +10515,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1140101629</t>
+          <t>1140114624</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -10551,13 +10523,13 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Plug screw</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Main Valve Assembly 00773405251600000</t>
+          <t>Upper Leveling Cylinder CBV Assembly 00773405213000000</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -10569,21 +10541,21 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1140101827</t>
+          <t>1140114625</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Build-up joint</t>
+          <t>Male stud connector</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
+          <t>Main Valve Assembly 00773405251600000</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -10595,7 +10567,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1140102936</t>
+          <t>1140114839</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -10603,13 +10575,13 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>High pressure articulating joint</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Telescopic Cylinder CBV Assembly 00773405213800000</t>
+          <t>Jib Cylinder CBV Assembly 00773405213200000</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -10621,7 +10593,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1140103405</t>
+          <t>1140115016</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -10629,13 +10601,13 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>45°Build-up joint</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Emergency Pump Assembly 00773405255200000</t>
+          <t>Hydraulic Pump Assembly 00773405250400000</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -10647,21 +10619,21 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1140107481</t>
+          <t>1140115620</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>Long male stud connector</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
-          <t>High Pressure Filter Assembly 0077340521100000</t>
+          <t>Steering Priority Valve Assembly 00773405215000000</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -10673,21 +10645,21 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1140107825</t>
+          <t>1990300400</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Male stud connector</t>
+          <t>U type tape</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Hydraulic Tank Assembly 00773405210200000</t>
+          <t>Tower Boom Assembly 00773400410000000</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -10699,7 +10671,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1140111252</t>
+          <t>1990300401</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -10707,13 +10679,13 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Reducer union</t>
+          <t>U-SHAPE TAPE</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -10725,466 +10697,24 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1140111483</t>
+          <t>204060296</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Reducer union</t>
+          <t>Great Wall Vehicle gear oil</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
+          <t>Chassis 00773402830000000</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>1140112820</t>
-        </is>
-      </c>
-      <c r="B378" t="n">
-        <v>1</v>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>Male stud connector</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr"/>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>1140112827</t>
-        </is>
-      </c>
-      <c r="B379" t="n">
-        <v>5</v>
-      </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>Male stud connector</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
-      <c r="E379" t="inlineStr">
-        <is>
-          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000; Emergency Pump Assembly 00773405255200000</t>
-        </is>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>1140113796</t>
-        </is>
-      </c>
-      <c r="B380" t="n">
-        <v>1</v>
-      </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>Build-up joint</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr"/>
-      <c r="E380" t="inlineStr">
-        <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>1140114034</t>
-        </is>
-      </c>
-      <c r="B381" t="n">
-        <v>1</v>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>Hydraulic pipe joint</t>
-        </is>
-      </c>
-      <c r="D381" t="inlineStr"/>
-      <c r="E381" t="inlineStr">
-        <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>1140114035</t>
-        </is>
-      </c>
-      <c r="B382" t="n">
-        <v>1</v>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>Hydraulic pipe joint</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr"/>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>1140114036</t>
-        </is>
-      </c>
-      <c r="B383" t="n">
-        <v>3</v>
-      </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>Hydraulic pipe joint; Male stud connector</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr"/>
-      <c r="E383" t="inlineStr">
-        <is>
-          <t>Steering Priority Valve Assembly 00773405215000000; Central Revolving Joint Assembly 00773405210800000</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>1140114040</t>
-        </is>
-      </c>
-      <c r="B384" t="n">
-        <v>9</v>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>Male stud connector</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
-      <c r="E384" t="inlineStr">
-        <is>
-          <t>Main Valve Assembly 00773405251600000; Main Boom Cylinder CBV Assembly 00773405253400000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>1140114046</t>
-        </is>
-      </c>
-      <c r="B385" t="n">
-        <v>3</v>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>T-junction</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>Lower Leveling Cylinder CBV Assembly 00773405212800000; Tower Boom Cylinder CBV Assembly 00773405253600000</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>1140114187</t>
-        </is>
-      </c>
-      <c r="B386" t="n">
-        <v>2</v>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>Test joint</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>Steering Priority Valve Assembly 00773405215000000; Main Valve Assembly 00773405251600000</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>1140114624</t>
-        </is>
-      </c>
-      <c r="B387" t="n">
-        <v>2</v>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>Male stud connector</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr"/>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>Upper Leveling Cylinder CBV Assembly 00773405213000000</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>1140114625</t>
-        </is>
-      </c>
-      <c r="B388" t="n">
-        <v>3</v>
-      </c>
-      <c r="C388" t="inlineStr">
-        <is>
-          <t>Male stud connector</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr"/>
-      <c r="E388" t="inlineStr">
-        <is>
-          <t>Main Valve Assembly 00773405251600000</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>1140114839</t>
-        </is>
-      </c>
-      <c r="B389" t="n">
-        <v>2</v>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>High pressure articulating joint</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr"/>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>Jib Cylinder CBV Assembly 00773405213200000</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>1140115016</t>
-        </is>
-      </c>
-      <c r="B390" t="n">
-        <v>1</v>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>45°Build-up joint</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr"/>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>Hydraulic Pump Assembly 00773405250400000</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>1140115620</t>
-        </is>
-      </c>
-      <c r="B391" t="n">
-        <v>1</v>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>Long male stud connector</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr"/>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>Steering Priority Valve Assembly 00773405215000000</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>1990300400</t>
-        </is>
-      </c>
-      <c r="B392" t="n">
-        <v>2</v>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>U type tape</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr"/>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>Tower Boom Assembly 00773400410000000</t>
-        </is>
-      </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>1990300401</t>
-        </is>
-      </c>
-      <c r="B393" t="n">
-        <v>1</v>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>U-SHAPE TAPE</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr"/>
-      <c r="E393" t="inlineStr">
-        <is>
-          <t>Chassis 00773402830000000</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>ZA14JE-Li</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>204060296</t>
-        </is>
-      </c>
-      <c r="B394" t="n">
-        <v>4</v>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>Great Wall Vehicle gear oil</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr"/>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>Chassis 00773402830000000</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
         <is>
           <t>ZA14JE-Li</t>
         </is>
